--- a/public/exports/29189838.xlsx
+++ b/public/exports/29189838.xlsx
@@ -231,7 +231,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5031663</t>
+          <t xml:space="preserve">308654</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -240,7 +240,7 @@
         </is>
       </c>
       <c r="F5">
-        <v>277</v>
+        <v>963</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032515</t>
+          <t xml:space="preserve">310746</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F6">
-        <v>555</v>
+        <v>912</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036402</t>
+          <t xml:space="preserve">310785, 310786</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -340,7 +340,7 @@
         </is>
       </c>
       <c r="F7">
-        <v>598</v>
+        <v>1804</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,7 +381,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037335</t>
+          <t xml:space="preserve">312110, 312111</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -390,7 +390,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>682</v>
+        <v>5025</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040463</t>
+          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="F9">
-        <v>407</v>
+        <v>6338</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041709</t>
+          <t xml:space="preserve">5031663</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="F10">
-        <v>335</v>
+        <v>277</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041952</t>
+          <t xml:space="preserve">5032515</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F11">
-        <v>1988</v>
+        <v>555</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5042272</t>
+          <t xml:space="preserve">5036402</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F12">
-        <v>261</v>
+        <v>598</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5045221</t>
+          <t xml:space="preserve">5037335</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="F13">
-        <v>843</v>
+        <v>682</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5045221</t>
+          <t xml:space="preserve">5040463</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F14">
-        <v>765</v>
+        <v>407</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5045221</t>
+          <t xml:space="preserve">5041709</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>912</v>
+        <v>335</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5045221</t>
+          <t xml:space="preserve">5041952</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>321</v>
+        <v>1988</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185579</t>
+          <t xml:space="preserve">5042272</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F17">
-        <v>628</v>
+        <v>261</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195366</t>
+          <t xml:space="preserve">5045221</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F18">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197924</t>
+          <t xml:space="preserve">5045221</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F19">
-        <v>480</v>
+        <v>765</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5045221</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F20">
-        <v>432</v>
+        <v>912</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5045221</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F21">
-        <v>604</v>
+        <v>321</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5195366</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="F22">
-        <v>1293</v>
+        <v>855</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5197924</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>737</v>
+        <v>480</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">737284, 1806166</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="F24">
-        <v>1491</v>
+        <v>951</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7013286</t>
+          <t xml:space="preserve">737342, 5198528</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>665</v>
+        <v>357</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7013286</t>
+          <t xml:space="preserve">737347, 5201083</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F26">
-        <v>990</v>
+        <v>299</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">737284, 1806166</t>
+          <t xml:space="preserve">737357, 9198479</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>951</v>
+        <v>453</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">737306, 8669930</t>
+          <t xml:space="preserve">7631694</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">102</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>287</v>
+        <v>1024</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">737335, 5186260</t>
+          <t xml:space="preserve">8097597</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="F29">
-        <v>2295</v>
+        <v>1594</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">737335, 5186260</t>
+          <t xml:space="preserve">9075418</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F30">
-        <v>303</v>
+        <v>1392</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">737342, 5198528</t>
+          <t xml:space="preserve">9075418</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F31">
-        <v>357</v>
+        <v>709</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">737347, 5201083</t>
+          <t xml:space="preserve">9075418</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F32">
-        <v>299</v>
+        <v>443</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">737357, 9198479</t>
+          <t xml:space="preserve">9075418</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F33">
-        <v>453</v>
+        <v>629</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">737384, 5034272</t>
+          <t xml:space="preserve">9075418</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F34">
-        <v>439</v>
+        <v>358</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">737384, 5034272</t>
+          <t xml:space="preserve">9533877</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>842</v>
+        <v>488</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,30 +1781,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7631694</t>
+          <t xml:space="preserve">9361413</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="F36">
-        <v>1024</v>
+        <v>1505</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014636</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-08</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1831,30 +1831,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">7013286</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F37">
-        <v>328</v>
+        <v>665</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020371</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-14</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1881,30 +1881,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097597</t>
+          <t xml:space="preserve">7013286</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F38">
-        <v>1594</v>
+        <v>990</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020371</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1931,30 +1931,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9075418</t>
+          <t xml:space="preserve">5031659</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>1392</v>
+        <v>5190</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200055867</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-12-14</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -1981,30 +1981,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">9075418</t>
+          <t xml:space="preserve">5019020</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>709</v>
+        <v>1666</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311005200</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-06-24</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2031,30 +2031,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">9075418</t>
+          <t xml:space="preserve">737384, 5034272</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F41">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311010529</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-07-31</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9075418</t>
+          <t xml:space="preserve">737384, 5034272</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F42">
-        <v>629</v>
+        <v>842</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311010529</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-07-31</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2131,30 +2131,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9075418</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F43">
-        <v>358</v>
+        <v>432</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311012127</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2181,30 +2181,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9361413</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F44">
-        <v>1505</v>
+        <v>604</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311012127</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2231,30 +2231,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9533877</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F45">
-        <v>488</v>
+        <v>1293</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311012127</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2281,25 +2281,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198523</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F46">
-        <v>2744</v>
+        <v>737</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055008</t>
+          <t xml:space="preserve">311012127</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-18</t>
+          <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5031659</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F47">
-        <v>5190</v>
+        <v>1491</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055867</t>
+          <t xml:space="preserve">311012127</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-14</t>
+          <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">312110, 312111</t>
+          <t xml:space="preserve">737361, 5200702</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F48">
-        <v>5025</v>
+        <v>1045</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">310001043</t>
+          <t xml:space="preserve">311012722</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-07-09</t>
+          <t xml:space="preserve">2023-08-19</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019020</t>
+          <t xml:space="preserve">5033256</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F49">
-        <v>1666</v>
+        <v>660</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311005200</t>
+          <t xml:space="preserve">311022030</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-06-24</t>
+          <t xml:space="preserve">2023-10-14</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">737361, 5200702</t>
+          <t xml:space="preserve">5033256</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F50">
-        <v>1045</v>
+        <v>506</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311012722</t>
+          <t xml:space="preserve">311022030</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-19</t>
+          <t xml:space="preserve">2023-10-14</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,20 +2531,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5033256</t>
+          <t xml:space="preserve">5200702</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F51">
-        <v>660</v>
+        <v>1147</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311022030</t>
+          <t xml:space="preserve">311022029</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2581,20 +2581,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5033256</t>
+          <t xml:space="preserve">5200702</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F52">
-        <v>506</v>
+        <v>325</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311022030</t>
+          <t xml:space="preserve">311022029</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200702</t>
+          <t xml:space="preserve">5200088</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,16 +2640,16 @@
         </is>
       </c>
       <c r="F53">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311022029</t>
+          <t xml:space="preserve">311023566</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-14</t>
+          <t xml:space="preserve">2023-10-24</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200702</t>
+          <t xml:space="preserve">5185579</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F54">
-        <v>325</v>
+        <v>628</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311022029</t>
+          <t xml:space="preserve">311041631</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-14</t>
+          <t xml:space="preserve">2024-03-07</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">5198523</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>443</v>
+        <v>2744</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311023570</t>
+          <t xml:space="preserve">311082086</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-24</t>
+          <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200088</t>
+          <t xml:space="preserve">737306, 8669930</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">102</t>
         </is>
       </c>
       <c r="F56">
-        <v>1152</v>
+        <v>287</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311023566</t>
+          <t xml:space="preserve">311134619</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-24</t>
+          <t xml:space="preserve">2025-09-15</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">7013286</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F65">
-        <v>386</v>
+        <v>471</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242112</t>
+          <t xml:space="preserve">311245718</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-05</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">1806208</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F66">
-        <v>386</v>
+        <v>1043</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242111</t>
+          <t xml:space="preserve">311247093</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-20</t>
+          <t xml:space="preserve">2027-05-12</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7013286</t>
+          <t xml:space="preserve">5040417</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F67">
-        <v>471</v>
+        <v>3896</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245718</t>
+          <t xml:space="preserve">311251363</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-05</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806208</t>
+          <t xml:space="preserve">5040417</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F68">
-        <v>1043</v>
+        <v>865</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247093</t>
+          <t xml:space="preserve">311322794</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-12</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040417</t>
+          <t xml:space="preserve">9219343</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="F69">
-        <v>3896</v>
+        <v>2618</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251363</t>
+          <t xml:space="preserve">311252778</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040417</t>
+          <t xml:space="preserve">9219343</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="F70">
-        <v>865</v>
+        <v>2939</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311322794</t>
+          <t xml:space="preserve">311252778</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3536,11 +3536,11 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F71">
-        <v>2618</v>
+        <v>2108</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3586,11 +3586,11 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F72">
-        <v>2939</v>
+        <v>2496</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3636,11 +3636,11 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F73">
-        <v>2108</v>
+        <v>421</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9219343</t>
+          <t xml:space="preserve">7012946</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>2496</v>
+        <v>558</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252778</t>
+          <t xml:space="preserve">311255406</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-09</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9219343</t>
+          <t xml:space="preserve">7012946</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F75">
-        <v>421</v>
+        <v>1000</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252778</t>
+          <t xml:space="preserve">311255406</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-09</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3786,11 +3786,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F76">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7012946</t>
+          <t xml:space="preserve">5032129</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77">
-        <v>1000</v>
+        <v>506</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255406</t>
+          <t xml:space="preserve">311256440</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7012946</t>
+          <t xml:space="preserve">5032443</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>547</v>
+        <v>656</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255406</t>
+          <t xml:space="preserve">311256832</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032129</t>
+          <t xml:space="preserve">8669930</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F79">
-        <v>506</v>
+        <v>313</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256440</t>
+          <t xml:space="preserve">311260191</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032443</t>
+          <t xml:space="preserve">5041442</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="F80">
-        <v>656</v>
+        <v>613</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256832</t>
+          <t xml:space="preserve">311260833</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-27</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8669930</t>
+          <t xml:space="preserve">5041442</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F81">
-        <v>313</v>
+        <v>1228</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260191</t>
+          <t xml:space="preserve">311260833</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,20 +4081,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041442</t>
+          <t xml:space="preserve">8669930</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F82">
-        <v>613</v>
+        <v>660</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260833</t>
+          <t xml:space="preserve">311260633</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4131,20 +4131,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041442</t>
+          <t xml:space="preserve">8669930</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F83">
-        <v>1228</v>
+        <v>1133</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260833</t>
+          <t xml:space="preserve">311260633</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4186,11 +4186,11 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F84">
-        <v>660</v>
+        <v>492</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4236,11 +4236,11 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F85">
-        <v>1133</v>
+        <v>943</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4286,11 +4286,11 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F86">
-        <v>492</v>
+        <v>579</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4336,11 +4336,11 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F87">
-        <v>943</v>
+        <v>498</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4386,11 +4386,11 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F88">
-        <v>579</v>
+        <v>491</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4436,11 +4436,11 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F89">
-        <v>498</v>
+        <v>260</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4481,20 +4481,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8669930</t>
+          <t xml:space="preserve">9197724</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F90">
-        <v>491</v>
+        <v>5783</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260633</t>
+          <t xml:space="preserve">311260838</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4531,20 +4531,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8669930</t>
+          <t xml:space="preserve">9197724</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F91">
-        <v>260</v>
+        <v>898</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260633</t>
+          <t xml:space="preserve">311260838</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197724</t>
+          <t xml:space="preserve">5032052</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4590,16 +4590,16 @@
         </is>
       </c>
       <c r="F92">
-        <v>5783</v>
+        <v>1486</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260838</t>
+          <t xml:space="preserve">311263313</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-27</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197724</t>
+          <t xml:space="preserve">5033675</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F93">
-        <v>898</v>
+        <v>576</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260838</t>
+          <t xml:space="preserve">311263304</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-27</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032052</t>
+          <t xml:space="preserve">5199461</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4690,16 +4690,16 @@
         </is>
       </c>
       <c r="F94">
-        <v>1486</v>
+        <v>534</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263313</t>
+          <t xml:space="preserve">311263807</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-27</t>
+          <t xml:space="preserve">2027-07-31</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5033675</t>
+          <t xml:space="preserve">5032122</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4740,16 +4740,16 @@
         </is>
       </c>
       <c r="F95">
-        <v>576</v>
+        <v>2219</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263304</t>
+          <t xml:space="preserve">311264871</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-27</t>
+          <t xml:space="preserve">2027-08-08</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5199461</t>
+          <t xml:space="preserve">5021136</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="F96">
-        <v>534</v>
+        <v>1098</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263807</t>
+          <t xml:space="preserve">311266265</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-31</t>
+          <t xml:space="preserve">2027-08-15</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032122</t>
+          <t xml:space="preserve">7013292</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F97">
-        <v>2219</v>
+        <v>4791</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264871</t>
+          <t xml:space="preserve">311267420</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-08</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021136</t>
+          <t xml:space="preserve">5032480</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4890,16 +4890,16 @@
         </is>
       </c>
       <c r="F98">
-        <v>1098</v>
+        <v>697</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266265</t>
+          <t xml:space="preserve">311271966</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-15</t>
+          <t xml:space="preserve">2027-09-10</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7013292</t>
+          <t xml:space="preserve">5032507</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F99">
-        <v>4791</v>
+        <v>393</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267420</t>
+          <t xml:space="preserve">311272508</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">310785, 310786</t>
+          <t xml:space="preserve">5185078</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="F100">
-        <v>1804</v>
+        <v>771</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267885</t>
+          <t xml:space="preserve">311272502</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032480</t>
+          <t xml:space="preserve">5198603</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5040,16 +5040,16 @@
         </is>
       </c>
       <c r="F101">
-        <v>697</v>
+        <v>634</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271966</t>
+          <t xml:space="preserve">311272510</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-10</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032507</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="F102">
-        <v>393</v>
+        <v>1006</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272508</t>
+          <t xml:space="preserve">311276139</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185078</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F103">
-        <v>771</v>
+        <v>1360</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272502</t>
+          <t xml:space="preserve">311276139</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198603</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F104">
-        <v>634</v>
+        <v>536</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272510</t>
+          <t xml:space="preserve">311276139</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">5185936</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="F105">
-        <v>1006</v>
+        <v>270</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311281954</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-11-02</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">8894116</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F106">
-        <v>1360</v>
+        <v>589</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311285343</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">5195702</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F107">
-        <v>536</v>
+        <v>695</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311286934</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-12-03</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185936</t>
+          <t xml:space="preserve">5185767</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="F108">
-        <v>270</v>
+        <v>765</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311281954</t>
+          <t xml:space="preserve">311287222</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-02</t>
+          <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8894116</t>
+          <t xml:space="preserve">5198440</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5440,16 +5440,16 @@
         </is>
       </c>
       <c r="F109">
-        <v>589</v>
+        <v>721</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285343</t>
+          <t xml:space="preserve">311287623</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195702</t>
+          <t xml:space="preserve">5039208</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5490,16 +5490,16 @@
         </is>
       </c>
       <c r="F110">
-        <v>695</v>
+        <v>3216</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286934</t>
+          <t xml:space="preserve">311288120</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-03</t>
+          <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185767</t>
+          <t xml:space="preserve">5019884</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="F111">
-        <v>765</v>
+        <v>442</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287222</t>
+          <t xml:space="preserve">311288925</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198440</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F112">
-        <v>721</v>
+        <v>1683</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287623</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039208</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F113">
-        <v>3216</v>
+        <v>1538</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288120</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-11</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019884</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F114">
-        <v>442</v>
+        <v>2669</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288925</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">8097596</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F115">
-        <v>1683</v>
+        <v>1087</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311289816</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">8097597</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F116">
-        <v>1538</v>
+        <v>1367</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311289821</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F117">
-        <v>2669</v>
+        <v>706</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097596</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F118">
-        <v>1087</v>
+        <v>1125</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289816</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097597</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F119">
-        <v>1367</v>
+        <v>1045</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289821</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5986,11 +5986,11 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F120">
-        <v>706</v>
+        <v>1150</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6036,11 +6036,11 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F121">
-        <v>1125</v>
+        <v>296</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6086,11 +6086,11 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F122">
-        <v>1045</v>
+        <v>645</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6136,11 +6136,11 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F123">
-        <v>1150</v>
+        <v>668</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6181,25 +6181,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F124">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311305978</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-03-30</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F125">
-        <v>645</v>
+        <v>293</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="F126">
-        <v>668</v>
+        <v>588</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,25 +6331,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">9196503</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F127">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311305978</t>
+          <t xml:space="preserve">311308332</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-30</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">5032097</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6390,16 +6390,16 @@
         </is>
       </c>
       <c r="F128">
-        <v>293</v>
+        <v>351</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311309220</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2028-04-18</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">9928625</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F129">
-        <v>588</v>
+        <v>825</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311309818</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196503</t>
+          <t xml:space="preserve">5041004</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F130">
-        <v>271</v>
+        <v>4946</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308332</t>
+          <t xml:space="preserve">311395853</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2029-08-30</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032097</t>
+          <t xml:space="preserve">5040356</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="F131">
-        <v>351</v>
+        <v>673</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309220</t>
+          <t xml:space="preserve">311450533</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-18</t>
+          <t xml:space="preserve">2030-07-20</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9928625</t>
+          <t xml:space="preserve">1484897</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="F132">
-        <v>825</v>
+        <v>2189</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309818</t>
+          <t xml:space="preserve">311529163</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002769</t>
+          <t xml:space="preserve">5036534</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6640,16 +6640,16 @@
         </is>
       </c>
       <c r="F133">
-        <v>294</v>
+        <v>1800</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329144</t>
+          <t xml:space="preserve">311529161</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-06</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041004</t>
+          <t xml:space="preserve">5196229</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F134">
-        <v>4946</v>
+        <v>1950</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395853</t>
+          <t xml:space="preserve">311529164</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-30</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
+          <t xml:space="preserve">8309304</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6740,16 +6740,16 @@
         </is>
       </c>
       <c r="F135">
-        <v>6338</v>
+        <v>4954</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402991</t>
+          <t xml:space="preserve">311529162</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-09</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040356</t>
+          <t xml:space="preserve">5197937</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6790,16 +6790,16 @@
         </is>
       </c>
       <c r="F136">
-        <v>673</v>
+        <v>1070</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311450533</t>
+          <t xml:space="preserve">311534227</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-20</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1484897</t>
+          <t xml:space="preserve">5197937</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F137">
-        <v>2189</v>
+        <v>326</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529163</t>
+          <t xml:space="preserve">311534227</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036534</t>
+          <t xml:space="preserve">10156994</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="F138">
-        <v>1800</v>
+        <v>325</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529161</t>
+          <t xml:space="preserve">311535979</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-14</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196229</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F139">
-        <v>1950</v>
+        <v>294</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529164</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8309304</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F140">
-        <v>4954</v>
+        <v>1558</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529162</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">308654</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F141">
-        <v>963</v>
+        <v>348</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533232</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197937</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7090,16 +7090,16 @@
         </is>
       </c>
       <c r="F142">
-        <v>1070</v>
+        <v>2285</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534227</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197937</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="F143">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534227</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">10156994</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F144">
-        <v>325</v>
+        <v>649</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535979</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-14</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F145">
-        <v>294</v>
+        <v>1337</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F146">
-        <v>1558</v>
+        <v>461</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F147">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">5198538</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7390,16 +7390,16 @@
         </is>
       </c>
       <c r="F148">
-        <v>2285</v>
+        <v>2208</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311543399</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F149">
-        <v>285</v>
+        <v>353</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F150">
-        <v>649</v>
+        <v>8186</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F151">
-        <v>1337</v>
+        <v>586</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F152">
-        <v>461</v>
+        <v>665</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F153">
-        <v>396</v>
+        <v>1625</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311547050</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198538</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F154">
-        <v>2208</v>
+        <v>339</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543399</t>
+          <t xml:space="preserve">311547065</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F155">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547018</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F156">
-        <v>8186</v>
+        <v>950</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311572718</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-24</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F157">
-        <v>586</v>
+        <v>1255</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F158">
-        <v>665</v>
+        <v>1422</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,25 +7931,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F159">
-        <v>1625</v>
+        <v>962</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547050</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F160">
-        <v>339</v>
+        <v>1499</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547065</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8040,16 +8040,16 @@
         </is>
       </c>
       <c r="F161">
-        <v>348</v>
+        <v>1232</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547018</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F162">
-        <v>950</v>
+        <v>838</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572718</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-24</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8136,11 +8136,11 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F163">
-        <v>1255</v>
+        <v>587</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -8186,11 +8186,11 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F164">
-        <v>1422</v>
+        <v>412</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F165">
-        <v>962</v>
+        <v>386</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311660921</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F166">
-        <v>1499</v>
+        <v>386</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311660921</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="F167">
-        <v>1232</v>
+        <v>328</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311660921</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">5043606</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F168">
-        <v>838</v>
+        <v>2188</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311740342</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">100002769</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F169">
-        <v>587</v>
+        <v>294</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311791576</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">5035619</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F170">
-        <v>412</v>
+        <v>315</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311814507</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">310746</t>
+          <t xml:space="preserve">5036533</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F171">
-        <v>912</v>
+        <v>2243</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730609</t>
+          <t xml:space="preserve">311894920</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5043606</t>
+          <t xml:space="preserve">5036533</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F172">
-        <v>2188</v>
+        <v>3900</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740342</t>
+          <t xml:space="preserve">311894909</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-21</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5035619</t>
+          <t xml:space="preserve">737305, 5019907</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F173">
-        <v>315</v>
+        <v>2050</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814507</t>
+          <t xml:space="preserve">311894926</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-28</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,25 +8681,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036533</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F174">
-        <v>2243</v>
+        <v>423</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894920</t>
+          <t xml:space="preserve">311895815</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036533</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F175">
-        <v>3900</v>
+        <v>1665</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894909</t>
+          <t xml:space="preserve">311896169</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">737305, 5019907</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F176">
-        <v>2050</v>
+        <v>273</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894926</t>
+          <t xml:space="preserve">311896606</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-04-24</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">737335, 5186260</t>
+          <t xml:space="preserve">5020950</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F177">
-        <v>537</v>
+        <v>1868</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894879</t>
+          <t xml:space="preserve">311905028</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,25 +8881,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F178">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895815</t>
+          <t xml:space="preserve">311905034</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">737370, 5037333</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F179">
-        <v>1665</v>
+        <v>953</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896169</t>
+          <t xml:space="preserve">311905030</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">737412, 5037833</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">104</t>
         </is>
       </c>
       <c r="F180">
-        <v>273</v>
+        <v>1348</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896606</t>
+          <t xml:space="preserve">311905034</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-24</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5020950</t>
+          <t xml:space="preserve">5195366</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9040,16 +9040,16 @@
         </is>
       </c>
       <c r="F181">
-        <v>1868</v>
+        <v>1052</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905028</t>
+          <t xml:space="preserve">311905369</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">737370, 5037333</t>
+          <t xml:space="preserve">737386, 5034767</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -9090,16 +9090,16 @@
         </is>
       </c>
       <c r="F182">
-        <v>953</v>
+        <v>452</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905030</t>
+          <t xml:space="preserve">311905606</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">737412, 5037833</t>
+          <t xml:space="preserve">9196089</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">104</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F183">
-        <v>1348</v>
+        <v>1782</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914611</t>
+          <t xml:space="preserve">311905611</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195366</t>
+          <t xml:space="preserve">737365, 5032515</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F184">
-        <v>1052</v>
+        <v>2937</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905369</t>
+          <t xml:space="preserve">311907452</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">737386, 5034767</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9240,16 +9240,16 @@
         </is>
       </c>
       <c r="F185">
-        <v>452</v>
+        <v>6676</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905606</t>
+          <t xml:space="preserve">311915214</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196089</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F186">
-        <v>1782</v>
+        <v>2183</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905611</t>
+          <t xml:space="preserve">311915210</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">737365, 5032515</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F187">
-        <v>2937</v>
+        <v>310</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907452</t>
+          <t xml:space="preserve">311915206</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9386,15 +9386,15 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F188">
-        <v>6676</v>
+        <v>907</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915214</t>
+          <t xml:space="preserve">311915205</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -9436,15 +9436,15 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F189">
-        <v>2183</v>
+        <v>1135</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915210</t>
+          <t xml:space="preserve">311915208</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -9486,15 +9486,15 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F190">
-        <v>310</v>
+        <v>1397</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915206</t>
+          <t xml:space="preserve">311915207</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9531,25 +9531,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">737335, 5186260</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F191">
-        <v>907</v>
+        <v>2295</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915205</t>
+          <t xml:space="preserve">311916957</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-08-03</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">737335, 5186260</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F192">
-        <v>1135</v>
+        <v>303</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915208</t>
+          <t xml:space="preserve">311916957</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-08-03</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">737335, 5186260</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F193">
-        <v>1397</v>
+        <v>537</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915207</t>
+          <t xml:space="preserve">311916957</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-08-03</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">

--- a/public/exports/29189838.xlsx
+++ b/public/exports/29189838.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenbro Allè 6</t>
+          <t xml:space="preserve">Byagervej 1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100049608</t>
+          <t xml:space="preserve">5032515</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H2">
-        <v>590</v>
+        <v>555</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 1A</t>
+          <t xml:space="preserve">Byagervej 3B</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10089969</t>
+          <t xml:space="preserve">9075418</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H3">
-        <v>799</v>
+        <v>358</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 1A</t>
+          <t xml:space="preserve">Byagervej 3C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10089969</t>
+          <t xml:space="preserve">9075418</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H4">
-        <v>841</v>
+        <v>629</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skodborg Nørregade 6</t>
+          <t xml:space="preserve">Byagervej 5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">308654</t>
+          <t xml:space="preserve">9075418</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H5">
-        <v>963</v>
+        <v>1392</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 110</t>
+          <t xml:space="preserve">Byagervej 5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">310746</t>
+          <t xml:space="preserve">9075418</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H6">
-        <v>912</v>
+        <v>709</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindeparken 26</t>
+          <t xml:space="preserve">Byagervej 5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">310785, 310786</t>
+          <t xml:space="preserve">9075418</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H7">
-        <v>1804</v>
+        <v>443</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,17 +451,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 50</t>
+          <t xml:space="preserve">Bøgelund 6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">312110, 312111</t>
+          <t xml:space="preserve">5045221</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="H8">
-        <v>5025</v>
+        <v>843</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 2</t>
+          <t xml:space="preserve">Bøgelund 6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
+          <t xml:space="preserve">5045221</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H9">
-        <v>6338</v>
+        <v>765</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 23</t>
+          <t xml:space="preserve">Bøgelund 6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5031663</t>
+          <t xml:space="preserve">5045221</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H10">
-        <v>277</v>
+        <v>912</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 1</t>
+          <t xml:space="preserve">Favrskovvej 8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032515</t>
+          <t xml:space="preserve">5037335</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H11">
-        <v>555</v>
+        <v>682</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,17 +691,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 73</t>
+          <t xml:space="preserve">Fuglesangsalle 10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036402</t>
+          <t xml:space="preserve">5041952</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="H12">
-        <v>598</v>
+        <v>1988</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,17 +751,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favrskovvej 8</t>
+          <t xml:space="preserve">Gammelengvej 17A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037335</t>
+          <t xml:space="preserve">737342, 5198528</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="H13">
-        <v>682</v>
+        <v>357</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,17 +811,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 2</t>
+          <t xml:space="preserve">Industriparken Nord 3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040463</t>
+          <t xml:space="preserve">737357, 9198479</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="H14">
-        <v>407</v>
+        <v>453</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelvej 2</t>
+          <t xml:space="preserve">Læborgvej 16B</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041709</t>
+          <t xml:space="preserve">737284, 1806166</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="H15">
-        <v>335</v>
+        <v>951</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglesangsalle 10</t>
+          <t xml:space="preserve">Parcelvej 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041952</t>
+          <t xml:space="preserve">5041709</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="H16">
-        <v>1988</v>
+        <v>335</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorupvænget 61</t>
+          <t xml:space="preserve">Rytterdam 1A</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5042272</t>
+          <t xml:space="preserve">10089969</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H17">
-        <v>261</v>
+        <v>799</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgelund 6</t>
+          <t xml:space="preserve">Rytterdam 1A</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5045221</t>
+          <t xml:space="preserve">10089969</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H18">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgelund 6</t>
+          <t xml:space="preserve">Rødding Engvej 1A</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5045221</t>
+          <t xml:space="preserve">5197924</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>765</v>
+        <v>480</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgelund 6</t>
+          <t xml:space="preserve">Rødding Engvej 5A</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5045221</t>
+          <t xml:space="preserve">7631694</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>912</v>
+        <v>1024</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 3</t>
+          <t xml:space="preserve">Skodborg Stadionvej 16A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5045221</t>
+          <t xml:space="preserve">9533877</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>321</v>
+        <v>488</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1351,26 +1351,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødding Engvej 1A</t>
+          <t xml:space="preserve">Skovvej 38</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197924</t>
+          <t xml:space="preserve">8097597</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H23">
-        <v>480</v>
+        <v>1594</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,26 +1411,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Læborgvej 16B</t>
+          <t xml:space="preserve">Stadionvej 3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">737284, 1806166</t>
+          <t xml:space="preserve">5045221</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H24">
-        <v>951</v>
+        <v>321</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,17 +1471,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelengvej 17A</t>
+          <t xml:space="preserve">Stenbro Allè 6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">737342, 5198528</t>
+          <t xml:space="preserve">100049608</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="H25">
-        <v>357</v>
+        <v>590</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,17 +1531,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ø Lindet Stadionvej 5</t>
+          <t xml:space="preserve">Storegade 73</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">737347, 5201083</t>
+          <t xml:space="preserve">5036402</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="H26">
-        <v>299</v>
+        <v>598</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,26 +1591,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industriparken Nord 3</t>
+          <t xml:space="preserve">Vorupvænget 61</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">737357, 9198479</t>
+          <t xml:space="preserve">5042272</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H27">
-        <v>453</v>
+        <v>261</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødding Engvej 5A</t>
+          <t xml:space="preserve">Ø Lindet Stadionvej 5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7631694</t>
+          <t xml:space="preserve">737347, 5201083</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="H28">
-        <v>1024</v>
+        <v>299</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 38</t>
+          <t xml:space="preserve">Østergade 2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,16 +1721,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097597</t>
+          <t xml:space="preserve">5040463</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H29">
-        <v>1594</v>
+        <v>407</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 5</t>
+          <t xml:space="preserve">Østre Alle 23</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9075418</t>
+          <t xml:space="preserve">5031663</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H30">
-        <v>1392</v>
+        <v>277</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 5</t>
+          <t xml:space="preserve">Fredensvej 3H</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,30 +1841,30 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9075418</t>
+          <t xml:space="preserve">9361413</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="H31">
-        <v>709</v>
+        <v>1505</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014636</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-08</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -1891,40 +1891,40 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 5</t>
+          <t xml:space="preserve">Lindegade 3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9075418</t>
+          <t xml:space="preserve">7013286</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H32">
-        <v>443</v>
+        <v>665</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020371</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-14</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -1951,40 +1951,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 3C</t>
+          <t xml:space="preserve">Østergade 4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9075418</t>
+          <t xml:space="preserve">7013286</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H33">
-        <v>629</v>
+        <v>990</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020371</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 3B</t>
+          <t xml:space="preserve">Magnolievej 28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,30 +2021,30 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">9075418</t>
+          <t xml:space="preserve">5031659</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>358</v>
+        <v>5190</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200055867</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-12-14</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skodborg Stadionvej 16A</t>
+          <t xml:space="preserve">Søndergade 50</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">9533877</t>
+          <t xml:space="preserve">312110, 312111</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="H35">
-        <v>488</v>
+        <v>5025</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310001043</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-07-09</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2131,35 +2131,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 3H</t>
+          <t xml:space="preserve">Østervang 20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9361413</t>
+          <t xml:space="preserve">5019020</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>1505</v>
+        <v>1666</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014636</t>
+          <t xml:space="preserve">311005200</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-08</t>
+          <t xml:space="preserve">2023-06-24</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,35 +2191,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegade 3</t>
+          <t xml:space="preserve">Åttevej 8A</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7013286</t>
+          <t xml:space="preserve">737384, 5034272</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H37">
-        <v>665</v>
+        <v>439</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020371</t>
+          <t xml:space="preserve">311010529</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-14</t>
+          <t xml:space="preserve">2023-07-31</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,35 +2251,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 4</t>
+          <t xml:space="preserve">Åttevej 8A</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">7013286</t>
+          <t xml:space="preserve">737384, 5034272</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H38">
-        <v>990</v>
+        <v>842</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020371</t>
+          <t xml:space="preserve">311010529</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-14</t>
+          <t xml:space="preserve">2023-07-31</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,35 +2311,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnolievej 28</t>
+          <t xml:space="preserve">Parkvej 4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5031659</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H39">
-        <v>5190</v>
+        <v>432</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055867</t>
+          <t xml:space="preserve">311012127</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-14</t>
+          <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,35 +2371,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 20</t>
+          <t xml:space="preserve">Parkvej 4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019020</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H40">
-        <v>1666</v>
+        <v>604</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311005200</t>
+          <t xml:space="preserve">311012127</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-06-24</t>
+          <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8A</t>
+          <t xml:space="preserve">Parkvej 4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">737384, 5034272</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H41">
-        <v>439</v>
+        <v>1293</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311010529</t>
+          <t xml:space="preserve">311012127</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-31</t>
+          <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8A</t>
+          <t xml:space="preserve">Parkvej 4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">737384, 5034272</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H42">
-        <v>842</v>
+        <v>737</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311010529</t>
+          <t xml:space="preserve">311012127</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-31</t>
+          <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4</t>
+          <t xml:space="preserve">Parkvej 4A</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2566,11 +2566,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H43">
-        <v>432</v>
+        <v>1491</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4</t>
+          <t xml:space="preserve">Øster Lindet Præstegårdsvej 18A</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,25 +2621,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">737361, 5200702</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H44">
-        <v>604</v>
+        <v>1045</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311012127</t>
+          <t xml:space="preserve">311012722</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-14</t>
+          <t xml:space="preserve">2023-08-19</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,35 +2671,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4</t>
+          <t xml:space="preserve">Bromindevej 3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5033256</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H45">
-        <v>1293</v>
+        <v>660</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311012127</t>
+          <t xml:space="preserve">311022030</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-14</t>
+          <t xml:space="preserve">2023-10-14</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4</t>
+          <t xml:space="preserve">Bromindevej 3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5033256</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H46">
-        <v>737</v>
+        <v>506</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311012127</t>
+          <t xml:space="preserve">311022030</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-14</t>
+          <t xml:space="preserve">2023-10-14</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4A</t>
+          <t xml:space="preserve">Øster Lindet Præstegårdsvej 18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,25 +2801,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5200702</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H47">
-        <v>1491</v>
+        <v>1147</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311012127</t>
+          <t xml:space="preserve">311022029</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-14</t>
+          <t xml:space="preserve">2023-10-14</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Lindet Præstegårdsvej 18A</t>
+          <t xml:space="preserve">Øster Lindet Præstegårdsvej 18</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,25 +2861,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">737361, 5200702</t>
+          <t xml:space="preserve">5200702</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H48">
-        <v>1045</v>
+        <v>325</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311012722</t>
+          <t xml:space="preserve">311022029</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-19</t>
+          <t xml:space="preserve">2023-10-14</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,35 +2911,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bromindevej 3</t>
+          <t xml:space="preserve">Skravevej 14</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5033256</t>
+          <t xml:space="preserve">5200088</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>660</v>
+        <v>1152</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311022030</t>
+          <t xml:space="preserve">311023566</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-14</t>
+          <t xml:space="preserve">2023-10-24</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,35 +2971,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bromindevej 3</t>
+          <t xml:space="preserve">Søvej 5A</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5033256</t>
+          <t xml:space="preserve">5185579</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H50">
-        <v>506</v>
+        <v>628</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311022030</t>
+          <t xml:space="preserve">311041631</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-14</t>
+          <t xml:space="preserve">2024-03-07</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Lindet Præstegårdsvej 18</t>
+          <t xml:space="preserve">Gammelengvej 6A</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200702</t>
+          <t xml:space="preserve">5198523</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="H51">
-        <v>1147</v>
+        <v>2744</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311022029</t>
+          <t xml:space="preserve">311082086</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-14</t>
+          <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,35 +3091,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Lindet Præstegårdsvej 18</t>
+          <t xml:space="preserve">Maltvej 84</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200702</t>
+          <t xml:space="preserve">737306, 8669930</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">102</t>
         </is>
       </c>
       <c r="H52">
-        <v>325</v>
+        <v>287</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311022029</t>
+          <t xml:space="preserve">311134619</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-14</t>
+          <t xml:space="preserve">2025-09-15</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skravevej 14</t>
+          <t xml:space="preserve">Kærhøjparken 11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200088</t>
+          <t xml:space="preserve">5040551</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,26 +3170,26 @@
         </is>
       </c>
       <c r="H53">
-        <v>1152</v>
+        <v>1048</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311023566</t>
+          <t xml:space="preserve">311231532</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-10-24</t>
+          <t xml:space="preserve">2027-03-01</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3211,45 +3211,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvej 5A</t>
+          <t xml:space="preserve">Gormsvej 8</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185579</t>
+          <t xml:space="preserve">5043490</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>628</v>
+        <v>425</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311041631</t>
+          <t xml:space="preserve">311237246</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-03-07</t>
+          <t xml:space="preserve">2027-03-28</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3271,17 +3271,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelengvej 6A</t>
+          <t xml:space="preserve">Jyllandsgade 2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198523</t>
+          <t xml:space="preserve">5041588</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3290,26 +3290,26 @@
         </is>
       </c>
       <c r="H55">
-        <v>2744</v>
+        <v>346</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082086</t>
+          <t xml:space="preserve">311237250</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-06</t>
+          <t xml:space="preserve">2027-03-28</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 84</t>
+          <t xml:space="preserve">Vorupvænget 4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,35 +3341,35 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">737306, 8669930</t>
+          <t xml:space="preserve">5042270</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">102</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H56">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311134619</t>
+          <t xml:space="preserve">311237257</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-15</t>
+          <t xml:space="preserve">2027-03-28</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærhøjparken 11</t>
+          <t xml:space="preserve">Damhus 9</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040551</t>
+          <t xml:space="preserve">5039051</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,16 +3410,16 @@
         </is>
       </c>
       <c r="H57">
-        <v>1048</v>
+        <v>284</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231532</t>
+          <t xml:space="preserve">311238334</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-01</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jyllandsgade 2</t>
+          <t xml:space="preserve">Lyngbakkevej 29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041588</t>
+          <t xml:space="preserve">9197482</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="H58">
-        <v>346</v>
+        <v>251</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237250</t>
+          <t xml:space="preserve">311238324</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-28</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorupvænget 4</t>
+          <t xml:space="preserve">Østervang 22</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5042270</t>
+          <t xml:space="preserve">5019014</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3530,16 +3530,16 @@
         </is>
       </c>
       <c r="H59">
-        <v>253</v>
+        <v>3417</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237257</t>
+          <t xml:space="preserve">311333468</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-28</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 8</t>
+          <t xml:space="preserve">Østervang 22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5043490</t>
+          <t xml:space="preserve">5019014</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H60">
-        <v>425</v>
+        <v>1187</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237246</t>
+          <t xml:space="preserve">311333468</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-28</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damhus 9</t>
+          <t xml:space="preserve">Østergade 4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,25 +3641,25 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039051</t>
+          <t xml:space="preserve">7013286</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H61">
-        <v>284</v>
+        <v>471</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238334</t>
+          <t xml:space="preserve">311245718</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-02</t>
+          <t xml:space="preserve">2027-05-05</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbakkevej 29</t>
+          <t xml:space="preserve">Kærhøjparken 19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197482</t>
+          <t xml:space="preserve">1806208</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="H62">
-        <v>251</v>
+        <v>1043</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238324</t>
+          <t xml:space="preserve">311247093</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-02</t>
+          <t xml:space="preserve">2027-05-12</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 22</t>
+          <t xml:space="preserve">Fr. d. 7's Gade 3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019014</t>
+          <t xml:space="preserve">5040417</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="H63">
-        <v>3417</v>
+        <v>3896</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311333468</t>
+          <t xml:space="preserve">311251363</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 22</t>
+          <t xml:space="preserve">Fr. d. 7's Gade 3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,25 +3821,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019014</t>
+          <t xml:space="preserve">5040417</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H64">
-        <v>1187</v>
+        <v>865</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311333468</t>
+          <t xml:space="preserve">311322794</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 4</t>
+          <t xml:space="preserve">Jacob Gades Alle 16</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7013286</t>
+          <t xml:space="preserve">9219343</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H65">
-        <v>471</v>
+        <v>2618</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245718</t>
+          <t xml:space="preserve">311252778</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-05</t>
+          <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærhøjparken 19</t>
+          <t xml:space="preserve">Jacob Gades Alle 16</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,25 +3941,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806208</t>
+          <t xml:space="preserve">9219343</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H66">
-        <v>1043</v>
+        <v>2939</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247093</t>
+          <t xml:space="preserve">311252778</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-12</t>
+          <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fr. d. 7's Gade 3</t>
+          <t xml:space="preserve">Jacob Gades Alle 16</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,25 +4001,25 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040417</t>
+          <t xml:space="preserve">9219343</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H67">
-        <v>3896</v>
+        <v>2108</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251363</t>
+          <t xml:space="preserve">311252778</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fr. d. 7's Gade 3</t>
+          <t xml:space="preserve">Jacob Gades Alle 16</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,25 +4061,25 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040417</t>
+          <t xml:space="preserve">9219343</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H68">
-        <v>865</v>
+        <v>2496</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311322794</t>
+          <t xml:space="preserve">311252778</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4126,11 +4126,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H69">
-        <v>2618</v>
+        <v>421</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacob Gades Alle 16</t>
+          <t xml:space="preserve">Baungårdsvej 2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9219343</t>
+          <t xml:space="preserve">7012946</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H70">
-        <v>2939</v>
+        <v>558</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252778</t>
+          <t xml:space="preserve">311255406</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-09</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacob Gades Alle 16</t>
+          <t xml:space="preserve">Baungårdsvej 2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,25 +4241,25 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9219343</t>
+          <t xml:space="preserve">7012946</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H71">
-        <v>2108</v>
+        <v>1000</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252778</t>
+          <t xml:space="preserve">311255406</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-09</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacob Gades Alle 16</t>
+          <t xml:space="preserve">Baungårdsvej 2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,25 +4301,25 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9219343</t>
+          <t xml:space="preserve">7012946</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H72">
-        <v>2496</v>
+        <v>547</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252778</t>
+          <t xml:space="preserve">311255406</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-09</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacob Gades Alle 16</t>
+          <t xml:space="preserve">Fredensvej 10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9219343</t>
+          <t xml:space="preserve">5032129</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>421</v>
+        <v>506</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252778</t>
+          <t xml:space="preserve">311256440</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-09</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baungårdsvej 2</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7012946</t>
+          <t xml:space="preserve">5032443</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,16 +4430,16 @@
         </is>
       </c>
       <c r="H74">
-        <v>558</v>
+        <v>656</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255406</t>
+          <t xml:space="preserve">311256832</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baungårdsvej 2</t>
+          <t xml:space="preserve">Maltvej 86</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7012946</t>
+          <t xml:space="preserve">8669930</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H75">
-        <v>1000</v>
+        <v>313</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255406</t>
+          <t xml:space="preserve">311260191</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baungårdsvej 2</t>
+          <t xml:space="preserve">Maltvej 86</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,25 +4541,25 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7012946</t>
+          <t xml:space="preserve">8669930</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>547</v>
+        <v>660</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255406</t>
+          <t xml:space="preserve">311260633</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 10</t>
+          <t xml:space="preserve">Maltvej 86</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032129</t>
+          <t xml:space="preserve">8669930</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H77">
-        <v>506</v>
+        <v>1133</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256440</t>
+          <t xml:space="preserve">311260633</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Maltvej 86</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032443</t>
+          <t xml:space="preserve">8669930</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H78">
-        <v>656</v>
+        <v>492</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256832</t>
+          <t xml:space="preserve">311260633</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-27</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4726,20 +4726,20 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H79">
-        <v>313</v>
+        <v>943</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260191</t>
+          <t xml:space="preserve">311260633</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Alle 92A</t>
+          <t xml:space="preserve">Maltvej 86</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,20 +4781,20 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041442</t>
+          <t xml:space="preserve">8669930</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H80">
-        <v>613</v>
+        <v>579</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260833</t>
+          <t xml:space="preserve">311260633</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Alle 92B</t>
+          <t xml:space="preserve">Maltvej 86</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041442</t>
+          <t xml:space="preserve">8669930</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,11 +4850,11 @@
         </is>
       </c>
       <c r="H81">
-        <v>1228</v>
+        <v>498</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260833</t>
+          <t xml:space="preserve">311260633</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4906,11 +4906,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H82">
-        <v>660</v>
+        <v>491</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4966,11 +4966,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H83">
-        <v>1133</v>
+        <v>260</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 86</t>
+          <t xml:space="preserve">Nygade 17</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,20 +5021,20 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8669930</t>
+          <t xml:space="preserve">9197724</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H84">
-        <v>492</v>
+        <v>5783</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260633</t>
+          <t xml:space="preserve">311260838</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 86</t>
+          <t xml:space="preserve">Nygade 17</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,20 +5081,20 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8669930</t>
+          <t xml:space="preserve">9197724</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H85">
-        <v>943</v>
+        <v>898</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260633</t>
+          <t xml:space="preserve">311260838</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 86</t>
+          <t xml:space="preserve">Øster Alle 92A</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,20 +5141,20 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8669930</t>
+          <t xml:space="preserve">5041442</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="H86">
-        <v>579</v>
+        <v>613</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260633</t>
+          <t xml:space="preserve">311260833</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 86</t>
+          <t xml:space="preserve">Øster Alle 92B</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8669930</t>
+          <t xml:space="preserve">5041442</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,11 +5210,11 @@
         </is>
       </c>
       <c r="H87">
-        <v>498</v>
+        <v>1228</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260633</t>
+          <t xml:space="preserve">311260833</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5251,35 +5251,35 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 86</t>
+          <t xml:space="preserve">Industrivej 15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8669930</t>
+          <t xml:space="preserve">5032052</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H88">
-        <v>491</v>
+        <v>1486</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260633</t>
+          <t xml:space="preserve">311263313</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-27</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,35 +5311,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 86</t>
+          <t xml:space="preserve">Vesterled 75</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8669930</t>
+          <t xml:space="preserve">5033675</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>260</v>
+        <v>576</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260633</t>
+          <t xml:space="preserve">311263304</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-27</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,17 +5371,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 17</t>
+          <t xml:space="preserve">Gl Vejenvej 2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197724</t>
+          <t xml:space="preserve">5199461</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="H90">
-        <v>5783</v>
+        <v>534</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260838</t>
+          <t xml:space="preserve">311263807</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-31</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,35 +5431,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 17</t>
+          <t xml:space="preserve">Fredensvej 3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197724</t>
+          <t xml:space="preserve">5032122</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H91">
-        <v>898</v>
+        <v>2219</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260838</t>
+          <t xml:space="preserve">311264871</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-08-08</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,17 +5491,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 15</t>
+          <t xml:space="preserve">Hovedgaden 2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032052</t>
+          <t xml:space="preserve">5021136</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5510,16 +5510,16 @@
         </is>
       </c>
       <c r="H92">
-        <v>1486</v>
+        <v>1098</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263313</t>
+          <t xml:space="preserve">311266265</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-27</t>
+          <t xml:space="preserve">2027-08-15</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,35 +5551,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 75</t>
+          <t xml:space="preserve">Askovvej 7</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5033675</t>
+          <t xml:space="preserve">7013292</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H93">
-        <v>576</v>
+        <v>4791</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263304</t>
+          <t xml:space="preserve">311267420</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-27</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Vejenvej 2</t>
+          <t xml:space="preserve">Lindeparken 26</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5199461</t>
+          <t xml:space="preserve">310785, 310786</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="H94">
-        <v>534</v>
+        <v>1804</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263807</t>
+          <t xml:space="preserve">311267885</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-31</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 3</t>
+          <t xml:space="preserve">Fabriksvej 11</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032122</t>
+          <t xml:space="preserve">5032480</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="H95">
-        <v>2219</v>
+        <v>697</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264871</t>
+          <t xml:space="preserve">311271966</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-08</t>
+          <t xml:space="preserve">2027-09-10</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 2</t>
+          <t xml:space="preserve">Dixensvej 3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021136</t>
+          <t xml:space="preserve">5185078</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="H96">
-        <v>1098</v>
+        <v>771</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266265</t>
+          <t xml:space="preserve">311272502</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-15</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,35 +5791,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askovvej 7</t>
+          <t xml:space="preserve">Jernbanegade 16</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">7013292</t>
+          <t xml:space="preserve">5032507</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H97">
-        <v>4791</v>
+        <v>393</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267420</t>
+          <t xml:space="preserve">311272508</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,17 +5851,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabriksvej 11</t>
+          <t xml:space="preserve">Vinkelvej 3</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032480</t>
+          <t xml:space="preserve">5198603</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5870,16 +5870,16 @@
         </is>
       </c>
       <c r="H98">
-        <v>697</v>
+        <v>634</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271966</t>
+          <t xml:space="preserve">311272510</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-10</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 16</t>
+          <t xml:space="preserve">Stadion Alle 2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032507</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>393</v>
+        <v>1006</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272508</t>
+          <t xml:space="preserve">311276139</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,35 +5971,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dixensvej 3</t>
+          <t xml:space="preserve">Stadion Alle 2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185078</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H100">
-        <v>771</v>
+        <v>1360</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272502</t>
+          <t xml:space="preserve">311276139</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 3</t>
+          <t xml:space="preserve">Stadion Alle 2</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198603</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H101">
-        <v>634</v>
+        <v>536</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272510</t>
+          <t xml:space="preserve">311276139</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 2</t>
+          <t xml:space="preserve">Jels Søndergade 17A</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">5185936</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6110,16 +6110,16 @@
         </is>
       </c>
       <c r="H102">
-        <v>1006</v>
+        <v>270</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311281954</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-11-02</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 2</t>
+          <t xml:space="preserve">Højmarksvej 18B</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">8894116</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>1360</v>
+        <v>589</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311285343</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,35 +6211,35 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 2</t>
+          <t xml:space="preserve">Skolegade 1B</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">5195702</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H104">
-        <v>536</v>
+        <v>695</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311286934</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-12-03</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jels Søndergade 17A</t>
+          <t xml:space="preserve">Dixensvej 1A</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185936</t>
+          <t xml:space="preserve">5185767</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="H105">
-        <v>270</v>
+        <v>765</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311281954</t>
+          <t xml:space="preserve">311287222</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-02</t>
+          <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18B</t>
+          <t xml:space="preserve">Nordre Industrivej 20</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8894116</t>
+          <t xml:space="preserve">5198440</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="H106">
-        <v>589</v>
+        <v>721</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285343</t>
+          <t xml:space="preserve">311287623</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,17 +6391,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1B</t>
+          <t xml:space="preserve">Maltvej 58</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195702</t>
+          <t xml:space="preserve">5039208</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6410,16 +6410,16 @@
         </is>
       </c>
       <c r="H107">
-        <v>695</v>
+        <v>3216</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286934</t>
+          <t xml:space="preserve">311288120</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-03</t>
+          <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,17 +6451,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dixensvej 1A</t>
+          <t xml:space="preserve">Møllevænget 3</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185767</t>
+          <t xml:space="preserve">5019884</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="H108">
-        <v>765</v>
+        <v>442</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287222</t>
+          <t xml:space="preserve">311288925</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,35 +6511,35 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Industrivej 20</t>
+          <t xml:space="preserve">Bakkevej 26</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198440</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H109">
-        <v>721</v>
+        <v>1538</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287623</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 58</t>
+          <t xml:space="preserve">Bakkevej 26</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039208</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H110">
-        <v>3216</v>
+        <v>2669</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288120</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-11</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,35 +6631,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 3</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019884</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H111">
-        <v>442</v>
+        <v>1683</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288925</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6701,25 +6701,25 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">8097596</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H112">
-        <v>1683</v>
+        <v>1087</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311289816</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 26</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6761,25 +6761,25 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">8097597</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H113">
-        <v>1538</v>
+        <v>1367</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311289821</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,35 +6811,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 26</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>2669</v>
+        <v>706</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,35 +6871,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097596</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H115">
-        <v>1087</v>
+        <v>1125</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289816</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,35 +6931,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097597</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H116">
-        <v>1367</v>
+        <v>1045</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289821</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7006,11 +7006,11 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H117">
-        <v>706</v>
+        <v>1150</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -7066,11 +7066,11 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H118">
-        <v>1125</v>
+        <v>296</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7126,11 +7126,11 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H119">
-        <v>1045</v>
+        <v>645</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7186,11 +7186,11 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H120">
-        <v>1150</v>
+        <v>668</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -7231,35 +7231,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H121">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311305978</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-03-30</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,35 +7291,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H122">
-        <v>645</v>
+        <v>293</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,17 +7351,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7370,16 +7370,16 @@
         </is>
       </c>
       <c r="H123">
-        <v>668</v>
+        <v>588</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,35 +7411,35 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Blomsterengen 43</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">9196503</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H124">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311305978</t>
+          <t xml:space="preserve">311308332</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-30</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">5032097</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="H125">
-        <v>293</v>
+        <v>351</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311309220</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2028-04-18</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,35 +7531,35 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Skolegade 7</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">9928625</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H126">
-        <v>588</v>
+        <v>825</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311309818</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,35 +7591,35 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomsterengen 43</t>
+          <t xml:space="preserve">Rådhuspassagen 3</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196503</t>
+          <t xml:space="preserve">5041004</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H127">
-        <v>271</v>
+        <v>4946</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308332</t>
+          <t xml:space="preserve">311395853</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2029-08-30</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Vestergade 2</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032097</t>
+          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7670,16 +7670,16 @@
         </is>
       </c>
       <c r="H128">
-        <v>351</v>
+        <v>6338</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309220</t>
+          <t xml:space="preserve">311402991</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-18</t>
+          <t xml:space="preserve">2029-10-09</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,17 +7711,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 7</t>
+          <t xml:space="preserve">Lindegade 10</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9928625</t>
+          <t xml:space="preserve">5040356</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7730,16 +7730,16 @@
         </is>
       </c>
       <c r="H129">
-        <v>825</v>
+        <v>673</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309818</t>
+          <t xml:space="preserve">311450533</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2030-07-20</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,35 +7771,35 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspassagen 3</t>
+          <t xml:space="preserve">Højmarksvej 20</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041004</t>
+          <t xml:space="preserve">5036534</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H130">
-        <v>4946</v>
+        <v>1800</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395853</t>
+          <t xml:space="preserve">311529161</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-30</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,17 +7831,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegade 10</t>
+          <t xml:space="preserve">Kirkepladsen 1</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6660</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040356</t>
+          <t xml:space="preserve">5196229</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7850,16 +7850,16 @@
         </is>
       </c>
       <c r="H131">
-        <v>673</v>
+        <v>1950</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311450533</t>
+          <t xml:space="preserve">311529164</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-20</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 15</t>
+          <t xml:space="preserve">Krygersvej 2</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1484897</t>
+          <t xml:space="preserve">8309304</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7910,11 +7910,11 @@
         </is>
       </c>
       <c r="H132">
-        <v>2189</v>
+        <v>4954</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529163</t>
+          <t xml:space="preserve">311529162</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7951,17 +7951,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 20</t>
+          <t xml:space="preserve">Stadionvej 15</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036534</t>
+          <t xml:space="preserve">1484897</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7970,11 +7970,11 @@
         </is>
       </c>
       <c r="H133">
-        <v>1800</v>
+        <v>2189</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529161</t>
+          <t xml:space="preserve">311529163</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkepladsen 1</t>
+          <t xml:space="preserve">Skodborg Nørregade 6</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6660</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196229</t>
+          <t xml:space="preserve">308654</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>1950</v>
+        <v>963</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529164</t>
+          <t xml:space="preserve">311533232</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krygersvej 2</t>
+          <t xml:space="preserve">Rødding Engvej 3</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8309304</t>
+          <t xml:space="preserve">5197937</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="H135">
-        <v>4954</v>
+        <v>1070</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529162</t>
+          <t xml:space="preserve">311534227</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8146,11 +8146,11 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H136">
-        <v>1070</v>
+        <v>326</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -8191,35 +8191,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødding Engvej 3</t>
+          <t xml:space="preserve">Industrivej Vest 18</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197937</t>
+          <t xml:space="preserve">10156994</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H137">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534227</t>
+          <t xml:space="preserve">311535979</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-07-14</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,35 +8251,35 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej Vest 18</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10156994</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H138">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535979</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-14</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8326,11 +8326,11 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H139">
-        <v>294</v>
+        <v>1558</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -8386,11 +8386,11 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H140">
-        <v>1558</v>
+        <v>348</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8441,25 +8441,25 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H141">
-        <v>348</v>
+        <v>2285</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8506,11 +8506,11 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H142">
-        <v>2285</v>
+        <v>285</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -8566,11 +8566,11 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H143">
-        <v>285</v>
+        <v>649</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -8626,11 +8626,11 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H144">
-        <v>649</v>
+        <v>1337</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -8686,11 +8686,11 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H145">
-        <v>1337</v>
+        <v>461</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -8746,11 +8746,11 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H146">
-        <v>461</v>
+        <v>396</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -8791,35 +8791,35 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Østergade 28</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">5198538</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H147">
-        <v>396</v>
+        <v>2208</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311543399</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 28</t>
+          <t xml:space="preserve">Rytterdam 1C</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198538</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -8870,16 +8870,16 @@
         </is>
       </c>
       <c r="H148">
-        <v>2208</v>
+        <v>353</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543399</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 1C</t>
+          <t xml:space="preserve">Rytterdam 9</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8926,11 +8926,11 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H149">
-        <v>353</v>
+        <v>8186</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -8986,11 +8986,11 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H150">
-        <v>8186</v>
+        <v>586</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -9046,11 +9046,11 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H151">
-        <v>586</v>
+        <v>665</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -9091,35 +9091,35 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 9</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H152">
-        <v>665</v>
+        <v>1625</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547050</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9166,15 +9166,15 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H153">
-        <v>1625</v>
+        <v>339</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547050</t>
+          <t xml:space="preserve">311547065</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9226,15 +9226,15 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H154">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547065</t>
+          <t xml:space="preserve">311547018</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9271,35 +9271,35 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Parkvej 4</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H155">
-        <v>348</v>
+        <v>950</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547018</t>
+          <t xml:space="preserve">311572718</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-24</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,17 +9331,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -9350,16 +9350,16 @@
         </is>
       </c>
       <c r="H156">
-        <v>950</v>
+        <v>1255</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572718</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-24</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9406,11 +9406,11 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H157">
-        <v>1255</v>
+        <v>1422</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -9466,11 +9466,11 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H158">
-        <v>1422</v>
+        <v>962</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -9526,11 +9526,11 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H159">
-        <v>962</v>
+        <v>1499</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -9586,11 +9586,11 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H160">
-        <v>1499</v>
+        <v>1232</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -9646,11 +9646,11 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H161">
-        <v>1232</v>
+        <v>838</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -9706,11 +9706,11 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H162">
-        <v>838</v>
+        <v>587</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -9766,11 +9766,11 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H163">
-        <v>587</v>
+        <v>412</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -9811,35 +9811,35 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Knudevejen 17A</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H164">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311660921</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17A</t>
+          <t xml:space="preserve">Knudevejen 17B</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="H166">
-        <v>386</v>
+        <v>328</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -9991,35 +9991,35 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17B</t>
+          <t xml:space="preserve">Borgergade 110</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">310746</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H167">
-        <v>328</v>
+        <v>912</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311730609</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10591,17 +10591,17 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 9A</t>
+          <t xml:space="preserve">Bækkevej 30</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5020950</t>
+          <t xml:space="preserve">737370, 5037333</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -10610,11 +10610,11 @@
         </is>
       </c>
       <c r="H177">
-        <v>1868</v>
+        <v>953</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905028</t>
+          <t xml:space="preserve">311905030</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10651,30 +10651,30 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 5</t>
+          <t xml:space="preserve">Bækkevej 9A</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">5020950</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H178">
-        <v>443</v>
+        <v>1868</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905034</t>
+          <t xml:space="preserve">311905028</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10711,30 +10711,30 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 30</t>
+          <t xml:space="preserve">Lindevej 5</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">737370, 5037333</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H179">
-        <v>953</v>
+        <v>443</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905030</t>
+          <t xml:space="preserve">311905034</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905034</t>
+          <t xml:space="preserve">311914611</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10831,17 +10831,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Holleskovvej 4</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195366</t>
+          <t xml:space="preserve">737386, 5034767</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="H181">
-        <v>1052</v>
+        <v>452</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905369</t>
+          <t xml:space="preserve">311905606</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10891,17 +10891,17 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holleskovvej 4</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">737386, 5034767</t>
+          <t xml:space="preserve">5195366</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10910,11 +10910,11 @@
         </is>
       </c>
       <c r="H182">
-        <v>452</v>
+        <v>1052</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905606</t>
+          <t xml:space="preserve">311905369</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">

--- a/public/exports/29189838.xlsx
+++ b/public/exports/29189838.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:M196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-08</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-14</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-14</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.K. Consult aps</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-14</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-07-09</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-06-24</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-07-31</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-07-31</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-08-14</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-08-19</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-10-14</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-10-14</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-10-14</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-10-14</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-10-24</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-03-07</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-15</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-01</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-28</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-28</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-28</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-05</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-12</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-27</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-27</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-31</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-08</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-15</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-10</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Herning Consult aps</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Herning Consult aps</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Herning Consult aps</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-02</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-03</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-30</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-18</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-30</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-09</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-07-20</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ankersen ApS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-14</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-24</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Murbyg ApS</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">Murbyg ApS</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Murbyg ApS</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-24</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-03</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-03</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-03</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,21 +12734,26 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L196"/>
+  <autoFilter ref="A1:M196"/>
 </worksheet>
 </file>
--- a/public/exports/29189838.xlsx
+++ b/public/exports/29189838.xlsx
@@ -4776,30 +4776,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Maltvej 86</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032443</t>
+          <t xml:space="preserve">8669930</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H74">
-        <v>656</v>
+        <v>313</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256832</t>
+          <t xml:space="preserve">311260191</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-27</t>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4856,15 +4856,15 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>313</v>
+        <v>660</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260191</t>
+          <t xml:space="preserve">311260633</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2027-07-13</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4921,11 +4921,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H76">
-        <v>660</v>
+        <v>1133</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4986,11 +4986,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H77">
-        <v>1133</v>
+        <v>492</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -5051,11 +5051,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H78">
-        <v>492</v>
+        <v>943</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -5116,11 +5116,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H79">
-        <v>943</v>
+        <v>579</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -5181,11 +5181,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H80">
-        <v>579</v>
+        <v>498</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -5246,11 +5246,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H81">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5311,11 +5311,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H82">
-        <v>491</v>
+        <v>260</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 86</t>
+          <t xml:space="preserve">Nygade 17</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5371,20 +5371,20 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8669930</t>
+          <t xml:space="preserve">9197724</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H83">
-        <v>260</v>
+        <v>5783</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260633</t>
+          <t xml:space="preserve">311260838</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5441,11 +5441,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H84">
-        <v>5783</v>
+        <v>898</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 17</t>
+          <t xml:space="preserve">Øster Alle 92A</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5501,20 +5501,20 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197724</t>
+          <t xml:space="preserve">5041442</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="H85">
-        <v>898</v>
+        <v>613</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260838</t>
+          <t xml:space="preserve">311260833</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Alle 92A</t>
+          <t xml:space="preserve">Øster Alle 92B</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5571,11 +5571,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H86">
-        <v>613</v>
+        <v>1228</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5621,30 +5621,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Alle 92B</t>
+          <t xml:space="preserve">Industrivej 15</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041442</t>
+          <t xml:space="preserve">5032052</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H87">
-        <v>1228</v>
+        <v>1486</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260833</t>
+          <t xml:space="preserve">311263313</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-13</t>
+          <t xml:space="preserve">2027-07-27</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 15</t>
+          <t xml:space="preserve">Vesterled 75</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032052</t>
+          <t xml:space="preserve">5033675</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5705,11 +5705,11 @@
         </is>
       </c>
       <c r="H88">
-        <v>1486</v>
+        <v>576</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263313</t>
+          <t xml:space="preserve">311263304</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5751,17 +5751,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 75</t>
+          <t xml:space="preserve">Gl Vejenvej 2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5033675</t>
+          <t xml:space="preserve">5199461</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5770,11 +5770,11 @@
         </is>
       </c>
       <c r="H89">
-        <v>576</v>
+        <v>534</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263304</t>
+          <t xml:space="preserve">311263807</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-27</t>
+          <t xml:space="preserve">2027-07-31</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Vejenvej 2</t>
+          <t xml:space="preserve">Fredensvej 3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5199461</t>
+          <t xml:space="preserve">5032122</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5835,11 +5835,11 @@
         </is>
       </c>
       <c r="H90">
-        <v>534</v>
+        <v>2219</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263807</t>
+          <t xml:space="preserve">311264871</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-31</t>
+          <t xml:space="preserve">2027-08-08</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5881,17 +5881,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 3</t>
+          <t xml:space="preserve">Hovedgaden 2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032122</t>
+          <t xml:space="preserve">5021136</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5900,11 +5900,11 @@
         </is>
       </c>
       <c r="H91">
-        <v>2219</v>
+        <v>1098</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264871</t>
+          <t xml:space="preserve">311266265</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-08</t>
+          <t xml:space="preserve">2027-08-15</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5946,30 +5946,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 2</t>
+          <t xml:space="preserve">Askovvej 7</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021136</t>
+          <t xml:space="preserve">7013292</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H92">
-        <v>1098</v>
+        <v>4791</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266265</t>
+          <t xml:space="preserve">311267420</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-15</t>
+          <t xml:space="preserve">2027-08-21</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6011,30 +6011,30 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askovvej 7</t>
+          <t xml:space="preserve">Lindeparken 26</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">7013292</t>
+          <t xml:space="preserve">310785, 310786</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H93">
-        <v>4791</v>
+        <v>1804</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267420</t>
+          <t xml:space="preserve">311267885</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-21</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6076,17 +6076,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindeparken 26</t>
+          <t xml:space="preserve">Fabriksvej 11</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">310785, 310786</t>
+          <t xml:space="preserve">5032480</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6095,11 +6095,11 @@
         </is>
       </c>
       <c r="H94">
-        <v>1804</v>
+        <v>697</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267885</t>
+          <t xml:space="preserve">311271966</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2027-09-10</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabriksvej 11</t>
+          <t xml:space="preserve">Dixensvej 3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032480</t>
+          <t xml:space="preserve">5185078</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6160,21 +6160,21 @@
         </is>
       </c>
       <c r="H95">
-        <v>697</v>
+        <v>771</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271966</t>
+          <t xml:space="preserve">311272502</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Herning Consult aps</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-10</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6206,17 +6206,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dixensvej 3</t>
+          <t xml:space="preserve">Jernbanegade 16</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185078</t>
+          <t xml:space="preserve">5032507</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6225,11 +6225,11 @@
         </is>
       </c>
       <c r="H96">
-        <v>771</v>
+        <v>393</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272502</t>
+          <t xml:space="preserve">311272508</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6271,17 +6271,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 16</t>
+          <t xml:space="preserve">Vinkelvej 3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032507</t>
+          <t xml:space="preserve">5198603</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6290,11 +6290,11 @@
         </is>
       </c>
       <c r="H97">
-        <v>393</v>
+        <v>634</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272508</t>
+          <t xml:space="preserve">311272510</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 3</t>
+          <t xml:space="preserve">Stadion Alle 2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198603</t>
+          <t xml:space="preserve">5021457</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6355,21 +6355,21 @@
         </is>
       </c>
       <c r="H98">
-        <v>634</v>
+        <v>1006</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272510</t>
+          <t xml:space="preserve">311276139</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Consult aps</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-10-02</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6416,11 +6416,11 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H99">
-        <v>1006</v>
+        <v>1360</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6481,11 +6481,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H100">
-        <v>1360</v>
+        <v>536</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6531,30 +6531,30 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 2</t>
+          <t xml:space="preserve">Jels Søndergade 17A</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021457</t>
+          <t xml:space="preserve">5185936</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H101">
-        <v>536</v>
+        <v>270</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276139</t>
+          <t xml:space="preserve">311281954</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-02</t>
+          <t xml:space="preserve">2027-11-02</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6596,17 +6596,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jels Søndergade 17A</t>
+          <t xml:space="preserve">Højmarksvej 18B</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185936</t>
+          <t xml:space="preserve">8894116</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6615,21 +6615,21 @@
         </is>
       </c>
       <c r="H102">
-        <v>270</v>
+        <v>589</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311281954</t>
+          <t xml:space="preserve">311285343</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-02</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18B</t>
+          <t xml:space="preserve">Skolegade 1B</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8894116</t>
+          <t xml:space="preserve">5195702</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6680,21 +6680,21 @@
         </is>
       </c>
       <c r="H103">
-        <v>589</v>
+        <v>695</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285343</t>
+          <t xml:space="preserve">311286934</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-03</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1B</t>
+          <t xml:space="preserve">Dixensvej 1A</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195702</t>
+          <t xml:space="preserve">5185767</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="H104">
-        <v>695</v>
+        <v>765</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286934</t>
+          <t xml:space="preserve">311287222</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-03</t>
+          <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dixensvej 1A</t>
+          <t xml:space="preserve">Nordre Industrivej 20</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5185767</t>
+          <t xml:space="preserve">5198440</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="H105">
-        <v>765</v>
+        <v>721</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287222</t>
+          <t xml:space="preserve">311287623</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Industrivej 20</t>
+          <t xml:space="preserve">Maltvej 58</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198440</t>
+          <t xml:space="preserve">5039208</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6875,11 +6875,11 @@
         </is>
       </c>
       <c r="H106">
-        <v>721</v>
+        <v>3216</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287623</t>
+          <t xml:space="preserve">311288120</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6921,17 +6921,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maltvej 58</t>
+          <t xml:space="preserve">Møllevænget 3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039208</t>
+          <t xml:space="preserve">5019884</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6940,11 +6940,11 @@
         </is>
       </c>
       <c r="H107">
-        <v>3216</v>
+        <v>442</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288120</t>
+          <t xml:space="preserve">311288925</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-11</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6986,30 +6986,30 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 3</t>
+          <t xml:space="preserve">Bakkevej 26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5019884</t>
+          <t xml:space="preserve">8097595</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H108">
-        <v>442</v>
+        <v>1538</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288925</t>
+          <t xml:space="preserve">311289326</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7066,11 +7066,11 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H109">
-        <v>1538</v>
+        <v>2669</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 26</t>
+          <t xml:space="preserve">Kærdalen 1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7131,11 +7131,11 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H110">
-        <v>2669</v>
+        <v>1683</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -7191,20 +7191,20 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097595</t>
+          <t xml:space="preserve">8097596</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H111">
-        <v>1683</v>
+        <v>1087</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289326</t>
+          <t xml:space="preserve">311289816</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097596</t>
+          <t xml:space="preserve">8097597</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7265,11 +7265,11 @@
         </is>
       </c>
       <c r="H112">
-        <v>1087</v>
+        <v>1367</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289816</t>
+          <t xml:space="preserve">311289821</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7311,17 +7311,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdalen 1</t>
+          <t xml:space="preserve">Vestergade 10</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097597</t>
+          <t xml:space="preserve">9197501</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7330,11 +7330,11 @@
         </is>
       </c>
       <c r="H113">
-        <v>1367</v>
+        <v>706</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289821</t>
+          <t xml:space="preserve">311290487</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7391,11 +7391,11 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H114">
-        <v>706</v>
+        <v>1125</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -7456,11 +7456,11 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H115">
-        <v>1125</v>
+        <v>1045</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -7521,11 +7521,11 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H116">
-        <v>1045</v>
+        <v>1150</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -7586,11 +7586,11 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H117">
-        <v>1150</v>
+        <v>296</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -7651,11 +7651,11 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H118">
-        <v>296</v>
+        <v>645</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7716,11 +7716,11 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H119">
-        <v>645</v>
+        <v>668</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7766,40 +7766,40 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 10</t>
+          <t xml:space="preserve">Skovvej 36</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9197501</t>
+          <t xml:space="preserve">9691651</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H120">
-        <v>668</v>
+        <v>265</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290487</t>
+          <t xml:space="preserve">311305978</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2028-03-30</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7846,15 +7846,15 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H121">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311305978</t>
+          <t xml:space="preserve">311307544</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-30</t>
+          <t xml:space="preserve">2028-04-10</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7911,11 +7911,11 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H122">
-        <v>293</v>
+        <v>588</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -7961,30 +7961,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 36</t>
+          <t xml:space="preserve">Blomsterengen 43</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691651</t>
+          <t xml:space="preserve">9196503</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H123">
-        <v>588</v>
+        <v>271</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307544</t>
+          <t xml:space="preserve">311308332</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-10</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8026,17 +8026,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomsterengen 43</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196503</t>
+          <t xml:space="preserve">5032097</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -8045,11 +8045,11 @@
         </is>
       </c>
       <c r="H124">
-        <v>271</v>
+        <v>351</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308332</t>
+          <t xml:space="preserve">311309220</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2028-04-18</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolegade 7</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032097</t>
+          <t xml:space="preserve">9928625</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8110,11 +8110,11 @@
         </is>
       </c>
       <c r="H125">
-        <v>351</v>
+        <v>825</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309220</t>
+          <t xml:space="preserve">311309818</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-18</t>
+          <t xml:space="preserve">2028-04-23</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8156,40 +8156,40 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 7</t>
+          <t xml:space="preserve">Rådhuspassagen 3</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9928625</t>
+          <t xml:space="preserve">5041004</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H126">
-        <v>825</v>
+        <v>4946</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311309818</t>
+          <t xml:space="preserve">311395853</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-23</t>
+          <t xml:space="preserve">2029-08-30</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspassagen 3</t>
+          <t xml:space="preserve">Vestergade 2</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8231,30 +8231,30 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5041004</t>
+          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H127">
-        <v>4946</v>
+        <v>6338</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395853</t>
+          <t xml:space="preserve">311402991</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-30</t>
+          <t xml:space="preserve">2029-10-09</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 2</t>
+          <t xml:space="preserve">Lindegade 10</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">434528, 434529, 434530, 434531, 434532, 434533, 434878, 434885, 434534, 434535, 434536, 434537, 434870, 434872, 434873, 434874, 434875, 434876, 434877, 434879, 434880, 434881, 434882, 434883, 434884, 434886, 434887, 434888, 434889, 434890, 434891</t>
+          <t xml:space="preserve">5040356</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -8305,11 +8305,11 @@
         </is>
       </c>
       <c r="H128">
-        <v>6338</v>
+        <v>673</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311402991</t>
+          <t xml:space="preserve">311450533</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-09</t>
+          <t xml:space="preserve">2030-07-20</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegade 10</t>
+          <t xml:space="preserve">Højmarksvej 20</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5040356</t>
+          <t xml:space="preserve">5036534</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8370,21 +8370,21 @@
         </is>
       </c>
       <c r="H129">
-        <v>673</v>
+        <v>1800</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311450533</t>
+          <t xml:space="preserve">311529161</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-20</t>
+          <t xml:space="preserve">2031-06-18</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 20</t>
+          <t xml:space="preserve">Kirkepladsen 1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6660</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036534</t>
+          <t xml:space="preserve">5196229</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8435,11 +8435,11 @@
         </is>
       </c>
       <c r="H130">
-        <v>1800</v>
+        <v>1950</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529161</t>
+          <t xml:space="preserve">311529164</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8481,17 +8481,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkepladsen 1</t>
+          <t xml:space="preserve">Krygersvej 2</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6660</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5196229</t>
+          <t xml:space="preserve">8309304</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8500,11 +8500,11 @@
         </is>
       </c>
       <c r="H131">
-        <v>1950</v>
+        <v>4954</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529164</t>
+          <t xml:space="preserve">311529162</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8546,17 +8546,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krygersvej 2</t>
+          <t xml:space="preserve">Stadionvej 15</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8309304</t>
+          <t xml:space="preserve">1484897</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8565,11 +8565,11 @@
         </is>
       </c>
       <c r="H132">
-        <v>4954</v>
+        <v>2189</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529162</t>
+          <t xml:space="preserve">311529163</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 15</t>
+          <t xml:space="preserve">Skodborg Nørregade 6</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1484897</t>
+          <t xml:space="preserve">308654</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8630,21 +8630,21 @@
         </is>
       </c>
       <c r="H133">
-        <v>2189</v>
+        <v>963</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529163</t>
+          <t xml:space="preserve">311533232</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-18</t>
+          <t xml:space="preserve">2031-07-02</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skodborg Nørregade 6</t>
+          <t xml:space="preserve">Rødding Engvej 3</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">308654</t>
+          <t xml:space="preserve">5197937</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8695,21 +8695,21 @@
         </is>
       </c>
       <c r="H134">
-        <v>963</v>
+        <v>1070</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311533232</t>
+          <t xml:space="preserve">311534227</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-02</t>
+          <t xml:space="preserve">2031-07-07</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8756,11 +8756,11 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H135">
-        <v>1070</v>
+        <v>326</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -8806,40 +8806,40 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødding Engvej 3</t>
+          <t xml:space="preserve">Industrivej Vest 18</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5197937</t>
+          <t xml:space="preserve">10156994</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H136">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534227</t>
+          <t xml:space="preserve">311535979</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-07</t>
+          <t xml:space="preserve">2031-07-14</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8871,40 +8871,40 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej Vest 18</t>
+          <t xml:space="preserve">Hovborgvej 1</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">10156994</t>
+          <t xml:space="preserve">5037992</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H137">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535979</t>
+          <t xml:space="preserve">311540206</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-14</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8951,11 +8951,11 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H138">
-        <v>294</v>
+        <v>1558</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -9016,11 +9016,11 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H139">
-        <v>1558</v>
+        <v>348</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovborgvej 1</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9076,20 +9076,20 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037992</t>
+          <t xml:space="preserve">5032058</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H140">
-        <v>348</v>
+        <v>2285</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540206</t>
+          <t xml:space="preserve">311541332</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-08-17</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9146,11 +9146,11 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H141">
-        <v>2285</v>
+        <v>285</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -9211,11 +9211,11 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H142">
-        <v>285</v>
+        <v>649</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -9276,11 +9276,11 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H143">
-        <v>649</v>
+        <v>1337</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -9341,11 +9341,11 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H144">
-        <v>1337</v>
+        <v>461</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -9406,11 +9406,11 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H145">
-        <v>461</v>
+        <v>396</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -9456,30 +9456,30 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Østergade 28</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5032058</t>
+          <t xml:space="preserve">5198538</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H146">
-        <v>396</v>
+        <v>2208</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311541332</t>
+          <t xml:space="preserve">311543399</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-17</t>
+          <t xml:space="preserve">2031-08-26</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 28</t>
+          <t xml:space="preserve">Rytterdam 1C</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198538</t>
+          <t xml:space="preserve">9252176</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -9540,11 +9540,11 @@
         </is>
       </c>
       <c r="H147">
-        <v>2208</v>
+        <v>353</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543399</t>
+          <t xml:space="preserve">311546545</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-26</t>
+          <t xml:space="preserve">2031-09-08</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 1C</t>
+          <t xml:space="preserve">Rytterdam 9</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9601,11 +9601,11 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H148">
-        <v>353</v>
+        <v>8186</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -9666,11 +9666,11 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H149">
-        <v>8186</v>
+        <v>586</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -9731,11 +9731,11 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H150">
-        <v>586</v>
+        <v>665</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -9781,30 +9781,30 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterdam 9</t>
+          <t xml:space="preserve">Åttevej 8</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9252176</t>
+          <t xml:space="preserve">5034272</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H151">
-        <v>665</v>
+        <v>1625</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311546545</t>
+          <t xml:space="preserve">311547050</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-08</t>
+          <t xml:space="preserve">2031-09-09</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9861,15 +9861,15 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H152">
-        <v>1625</v>
+        <v>339</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547050</t>
+          <t xml:space="preserve">311547065</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9926,15 +9926,15 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H153">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547065</t>
+          <t xml:space="preserve">311547018</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9976,30 +9976,30 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åttevej 8</t>
+          <t xml:space="preserve">Parkvej 4</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034272</t>
+          <t xml:space="preserve">5198848</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H154">
-        <v>348</v>
+        <v>950</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547018</t>
+          <t xml:space="preserve">311572718</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-09</t>
+          <t xml:space="preserve">2031-09-24</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 4</t>
+          <t xml:space="preserve">Højmarksvej 16</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5198848</t>
+          <t xml:space="preserve">5036460</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -10060,11 +10060,11 @@
         </is>
       </c>
       <c r="H155">
-        <v>950</v>
+        <v>1255</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572718</t>
+          <t xml:space="preserve">311560309</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-24</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10121,11 +10121,11 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H156">
-        <v>1255</v>
+        <v>1422</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -10186,11 +10186,11 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H157">
-        <v>1422</v>
+        <v>962</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -10251,11 +10251,11 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H158">
-        <v>962</v>
+        <v>1499</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -10316,11 +10316,11 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H159">
-        <v>1499</v>
+        <v>1232</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -10381,11 +10381,11 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H160">
-        <v>1232</v>
+        <v>838</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -10446,11 +10446,11 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H161">
-        <v>838</v>
+        <v>587</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -10511,11 +10511,11 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H162">
-        <v>587</v>
+        <v>412</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -10561,40 +10561,40 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 16</t>
+          <t xml:space="preserve">Knudevejen 17A</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036460</t>
+          <t xml:space="preserve">7813581</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H163">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560309</t>
+          <t xml:space="preserve">311660921</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Murbyg ApS</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2033-02-17</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17A</t>
+          <t xml:space="preserve">Knudevejen 17B</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H164">
@@ -10706,11 +10706,11 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="H165">
-        <v>386</v>
+        <v>328</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -10756,40 +10756,40 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knudevejen 17B</t>
+          <t xml:space="preserve">Borgergade 110</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">7813581</t>
+          <t xml:space="preserve">310746</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H166">
-        <v>328</v>
+        <v>912</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660921</t>
+          <t xml:space="preserve">311730609</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-17</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10821,30 +10821,30 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgergade 110</t>
+          <t xml:space="preserve">Drejervej 7</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">310746</t>
+          <t xml:space="preserve">5043606</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H167">
-        <v>912</v>
+        <v>2188</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730609</t>
+          <t xml:space="preserve">311740342</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drejervej 7</t>
+          <t xml:space="preserve">Rugholmvej 16</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5043606</t>
+          <t xml:space="preserve">100002769</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="H168">
-        <v>2188</v>
+        <v>294</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740342</t>
+          <t xml:space="preserve">311791576</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-21</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10951,17 +10951,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugholmvej 16</t>
+          <t xml:space="preserve">Vestergade 19</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6670</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002769</t>
+          <t xml:space="preserve">5035619</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -10970,21 +10970,21 @@
         </is>
       </c>
       <c r="H169">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791576</t>
+          <t xml:space="preserve">311814507</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-15</t>
+          <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 19</t>
+          <t xml:space="preserve">Højmarksvej 18</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5035619</t>
+          <t xml:space="preserve">5036533</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -11035,21 +11035,21 @@
         </is>
       </c>
       <c r="H170">
-        <v>315</v>
+        <v>2243</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814507</t>
+          <t xml:space="preserve">311894920</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-28</t>
+          <t xml:space="preserve">2036-04-17</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11096,15 +11096,15 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H171">
-        <v>2243</v>
+        <v>3900</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894920</t>
+          <t xml:space="preserve">311894909</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11146,17 +11146,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 18</t>
+          <t xml:space="preserve">Møllevænget 5</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6670</t>
+          <t xml:space="preserve">6622</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5036533</t>
+          <t xml:space="preserve">737305, 5019907</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -11165,11 +11165,11 @@
         </is>
       </c>
       <c r="H172">
-        <v>3900</v>
+        <v>2050</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894909</t>
+          <t xml:space="preserve">311894926</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11211,17 +11211,17 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevænget 5</t>
+          <t xml:space="preserve">Stadionvej 2A</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6622</t>
+          <t xml:space="preserve">6752</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">737305, 5019907</t>
+          <t xml:space="preserve">737383, 5045451</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -11230,11 +11230,11 @@
         </is>
       </c>
       <c r="H173">
-        <v>2050</v>
+        <v>423</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894926</t>
+          <t xml:space="preserve">311895815</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-17</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11291,15 +11291,15 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H174">
-        <v>423</v>
+        <v>1665</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895815</t>
+          <t xml:space="preserve">311896169</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11356,15 +11356,15 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H175">
-        <v>1665</v>
+        <v>273</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896169</t>
+          <t xml:space="preserve">311896606</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-04-24</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11406,30 +11406,30 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 2A</t>
+          <t xml:space="preserve">Bækkevej 30</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">6752</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">737383, 5045451</t>
+          <t xml:space="preserve">737370, 5037333</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H176">
-        <v>273</v>
+        <v>953</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896606</t>
+          <t xml:space="preserve">311905030</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-24</t>
+          <t xml:space="preserve">2036-06-01</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11471,17 +11471,17 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 30</t>
+          <t xml:space="preserve">Bækkevej 9A</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6621</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">737370, 5037333</t>
+          <t xml:space="preserve">5020950</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -11490,11 +11490,11 @@
         </is>
       </c>
       <c r="H177">
-        <v>953</v>
+        <v>1868</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905030</t>
+          <t xml:space="preserve">311905028</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11536,35 +11536,35 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkevej 9A</t>
+          <t xml:space="preserve">Lindevej 5</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6621</t>
+          <t xml:space="preserve">6682</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5020950</t>
+          <t xml:space="preserve">5037833</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H178">
-        <v>1868</v>
+        <v>443</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905028</t>
+          <t xml:space="preserve">311905034</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 5</t>
+          <t xml:space="preserve">Lindevej 7A</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11611,16 +11611,16 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037833</t>
+          <t xml:space="preserve">737412, 5037833</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">104</t>
         </is>
       </c>
       <c r="H179">
-        <v>443</v>
+        <v>1348</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -11666,30 +11666,30 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 7A</t>
+          <t xml:space="preserve">Holleskovvej 4</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6682</t>
+          <t xml:space="preserve">6683</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">737412, 5037833</t>
+          <t xml:space="preserve">737386, 5034767</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">104</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H180">
-        <v>1348</v>
+        <v>452</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914611</t>
+          <t xml:space="preserve">311905606</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-01</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11731,17 +11731,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holleskovvej 4</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6683</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">737386, 5034767</t>
+          <t xml:space="preserve">5195366</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -11750,11 +11750,11 @@
         </is>
       </c>
       <c r="H181">
-        <v>452</v>
+        <v>1052</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905606</t>
+          <t xml:space="preserve">311905369</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Søndergyden 17</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5195366</t>
+          <t xml:space="preserve">9196089</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -11815,11 +11815,11 @@
         </is>
       </c>
       <c r="H182">
-        <v>1052</v>
+        <v>1782</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905369</t>
+          <t xml:space="preserve">311905611</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11861,30 +11861,30 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergyden 17</t>
+          <t xml:space="preserve">Byagervej 3</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9196089</t>
+          <t xml:space="preserve">737365, 5032515</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H183">
-        <v>1782</v>
+        <v>2937</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905611</t>
+          <t xml:space="preserve">311907452</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11926,30 +11926,30 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 3</t>
+          <t xml:space="preserve">Petersmindevej 1</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">737365, 5032515</t>
+          <t xml:space="preserve">7955800</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H184">
-        <v>2937</v>
+        <v>6676</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907452</t>
+          <t xml:space="preserve">311915214</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-07-20</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -12006,15 +12006,15 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H185">
-        <v>6676</v>
+        <v>2183</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915214</t>
+          <t xml:space="preserve">311915210</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12071,15 +12071,15 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H186">
-        <v>2183</v>
+        <v>310</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915210</t>
+          <t xml:space="preserve">311915206</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -12136,15 +12136,15 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H187">
-        <v>310</v>
+        <v>907</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915206</t>
+          <t xml:space="preserve">311915205</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12201,15 +12201,15 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H188">
-        <v>907</v>
+        <v>1135</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915205</t>
+          <t xml:space="preserve">311915208</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12266,15 +12266,15 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H189">
-        <v>1135</v>
+        <v>1397</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915208</t>
+          <t xml:space="preserve">311915207</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12316,30 +12316,30 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 1</t>
+          <t xml:space="preserve">Ørstedvej 10</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6630</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">7955800</t>
+          <t xml:space="preserve">737335, 5186260</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H190">
-        <v>1397</v>
+        <v>2295</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915207</t>
+          <t xml:space="preserve">311916957</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-20</t>
+          <t xml:space="preserve">2036-08-03</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12396,11 +12396,11 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H191">
-        <v>2295</v>
+        <v>303</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -12461,11 +12461,11 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H192">
-        <v>303</v>
+        <v>537</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -12511,40 +12511,40 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 10</t>
+          <t xml:space="preserve">Petersmindevej 2A</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6630</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">737335, 5186260</t>
+          <t xml:space="preserve">9203884</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="H193">
-        <v>537</v>
+        <v>1872</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916957</t>
+          <t xml:space="preserve">311922670</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-03</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12576,40 +12576,40 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petersmindevej 2A</t>
+          <t xml:space="preserve">Lille Veumvej 6</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9203884</t>
+          <t xml:space="preserve">5031183</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H194">
-        <v>1872</v>
+        <v>1056</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922670</t>
+          <t xml:space="preserve">311923191</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12641,17 +12641,17 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Veumvej 6</t>
+          <t xml:space="preserve">Ø. Skibelundvej 15</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6650</t>
+          <t xml:space="preserve">6600</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5031183</t>
+          <t xml:space="preserve">5039005</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -12660,11 +12660,11 @@
         </is>
       </c>
       <c r="H195">
-        <v>1056</v>
+        <v>326</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923191</t>
+          <t xml:space="preserve">311923198</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12706,17 +12706,17 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ø. Skibelundvej 15</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600</t>
+          <t xml:space="preserve">6650</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5039005</t>
+          <t xml:space="preserve">5032443</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -12725,11 +12725,11 @@
         </is>
       </c>
       <c r="H196">
-        <v>326</v>
+        <v>656</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923198</t>
+          <t xml:space="preserve">311924085</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-02</t>
+          <t xml:space="preserve">2036-09-07</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
